--- a/R/data/Final_Records_2501_0613.xlsx
+++ b/R/data/Final_Records_2501_0613.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kwlee/Documents/class202501/R/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D03E29BF-2CE1-1246-ACC3-C5A5E555587B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1685CD18-34F3-EE46-AF73-5C8687C5E9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" xr2:uid="{361C6A18-5925-554D-BD16-079B265C6283}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="22940" xr2:uid="{E52EA91A-9F0D-0745-9B87-697477CF9C75}"/>
   </bookViews>
   <sheets>
     <sheet name="성적" sheetId="1" r:id="rId1"/>
@@ -7382,10 +7382,10 @@
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="표준" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Heading" xfId="1" xr:uid="{EB9AB10E-AAA8-0545-961F-9BF8AF0E1C31}"/>
-    <cellStyle name="Heading1" xfId="2" xr:uid="{02760C67-02EC-C743-9E04-41F05C83F4E4}"/>
-    <cellStyle name="Result" xfId="3" xr:uid="{8F6F21EA-5CBB-6E4D-8D85-476C26E61C6D}"/>
-    <cellStyle name="Result2" xfId="4" xr:uid="{69C19523-590A-5E42-BE72-3EF984004D15}"/>
+    <cellStyle name="Heading" xfId="1" xr:uid="{313923A5-BFB3-354E-A659-2243D32E6445}"/>
+    <cellStyle name="Heading1" xfId="2" xr:uid="{89793E22-17B0-B648-B185-60AD9E514007}"/>
+    <cellStyle name="Result" xfId="3" xr:uid="{6BF5B4B3-8948-1646-8C83-26C6936D7656}"/>
+    <cellStyle name="Result2" xfId="4" xr:uid="{B6A289F8-92B8-C847-9177-654E44713E5C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7716,7 +7716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6723E8-9F9F-F44F-82FF-4977B2E993FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F51883-6C6D-7B4C-8A45-1E98FF83B2F5}">
   <dimension ref="A1:L597"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
@@ -12642,13 +12642,13 @@
         <v>575</v>
       </c>
       <c r="G130">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H130">
-        <v>27.43</v>
+        <v>29.57</v>
       </c>
       <c r="I130">
-        <v>18.29</v>
+        <v>19.71</v>
       </c>
       <c r="J130">
         <v>15.14</v>
@@ -12657,7 +12657,7 @@
         <v>10</v>
       </c>
       <c r="L130">
-        <v>88.86</v>
+        <v>94.43</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -14694,22 +14694,22 @@
         <v>793</v>
       </c>
       <c r="G184">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H184">
-        <v>11.82</v>
+        <v>13.54</v>
       </c>
       <c r="I184">
-        <v>8.86</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="J184">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="K184">
         <v>7.5</v>
       </c>
       <c r="L184">
-        <v>47.89</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -14770,22 +14770,22 @@
         <v>799</v>
       </c>
       <c r="G186">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H186">
-        <v>24.5</v>
+        <v>26.43</v>
       </c>
       <c r="I186">
-        <v>16.29</v>
+        <v>17.14</v>
       </c>
       <c r="J186">
-        <v>12.29</v>
+        <v>13.14</v>
       </c>
       <c r="K186">
         <v>10</v>
       </c>
       <c r="L186">
-        <v>81.069999999999993</v>
+        <v>86.71</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -17775,10 +17775,10 @@
         <v>20</v>
       </c>
       <c r="H265">
-        <v>27.86</v>
+        <v>30</v>
       </c>
       <c r="I265">
-        <v>18.29</v>
+        <v>19.71</v>
       </c>
       <c r="J265">
         <v>16.57</v>
@@ -17787,7 +17787,7 @@
         <v>10</v>
       </c>
       <c r="L265">
-        <v>92.71</v>
+        <v>96.29</v>
       </c>
     </row>
     <row r="266" spans="1:12">
@@ -19149,13 +19149,13 @@
         <v>19.71</v>
       </c>
       <c r="J301">
-        <v>14.29</v>
+        <v>15.71</v>
       </c>
       <c r="K301">
         <v>7.5</v>
       </c>
       <c r="L301">
-        <v>87.18</v>
+        <v>88.61</v>
       </c>
     </row>
     <row r="302" spans="1:12">
@@ -23586,7 +23586,7 @@
         <v>1714</v>
       </c>
       <c r="G418">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H418">
         <v>26.36</v>
@@ -23601,7 +23601,7 @@
         <v>8</v>
       </c>
       <c r="L418">
-        <v>77.5</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="419" spans="1:12">
@@ -24501,7 +24501,7 @@
         <v>20</v>
       </c>
       <c r="H442">
-        <v>26.57</v>
+        <v>28.71</v>
       </c>
       <c r="I442">
         <v>16.57</v>
@@ -24513,7 +24513,7 @@
         <v>9.5</v>
       </c>
       <c r="L442">
-        <v>85.5</v>
+        <v>87.64</v>
       </c>
     </row>
     <row r="443" spans="1:12">
